--- a/StructureDefinition-assistance-needs-profile.xlsx
+++ b/StructureDefinition-assistance-needs-profile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T01:45:26+00:00</t>
+    <t>2024-06-21T04:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
